--- a/test/data/all_data/bpbs_test_ok.xlsx
+++ b/test/data/all_data/bpbs_test_ok.xlsx
@@ -1488,7 +1488,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="193">
   <si>
     <t># ORANGE fields are mandatory. Your submission will fail if any mandatory fields are not completed.</t>
   </si>
@@ -2088,6 +2088,9 @@
   <si>
     <t>https://www.ddbj.nig.ac.jp</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>MTB313</t>
   </si>
 </sst>
 </file>
@@ -3403,7 +3406,7 @@
         <v>181</v>
       </c>
       <c r="S15" s="23" t="s">
-        <v>173</v>
+        <v>192</v>
       </c>
       <c r="T15" s="23" t="s">
         <v>182</v>
